--- a/CAISSE_VICTOR_HUGO_08-2026.xlsx
+++ b/CAISSE_VICTOR_HUGO_08-2026.xlsx
@@ -205,7 +205,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Total des charges du mois (budget) divisé par 30 jours. En dessous de ce chiffre de recette, la journée est déficitaire.</t>
+          <t xml:space="preserve">Ce que vous prévoyez de dépenser en marchandise sur le mois (café, eau, épicerie, boulangerie, nettoyage). La valeur par défaut, 20 500 DH, vient de l’ancien classeur (feuille CHARGE). Attention : en août 2026 le réalisé a été de 24 529 DH, nettoyage compris. Ce chiffre ne sert qu’au seuil de rentabilité ci-dessous, mais il le change beaucoup : ajustez-le à votre réalité.</t>
         </r>
       </text>
     </comment>
@@ -217,11 +217,23 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">Charges fixes + salaires + achats de marchandise, en budget, divisés par 30 jours. En dessous de ce chiffre de recette, la journée est déficitaire.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C41" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Recette du mois divisée par le nombre de jours réellement saisis.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C41" authorId="0">
+    <comment ref="C42" authorId="0">
       <text>
         <r>
           <rPr>
@@ -238,7 +250,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2111" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="164">
   <si>
     <t xml:space="preserve">TABLEAU DE BORD</t>
   </si>
@@ -654,6 +666,9 @@
   </si>
   <si>
     <t xml:space="preserve">LE CAFÉ COUVRE-T-IL SES CHARGES ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget achats de marchandise (par mois)</t>
   </si>
   <si>
     <t xml:space="preserve">Recette minimum par jour (seuil de rentabilité)</t>
@@ -1478,7 +1493,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="115">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1863,6 +1878,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="44" fillId="7" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="46" fillId="8" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2689,11 +2708,11 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="0"/>
-        <c:axId val="43260509"/>
-        <c:axId val="56180279"/>
+        <c:axId val="55383104"/>
+        <c:axId val="65178294"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="43260509"/>
+        <c:axId val="55383104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2725,7 +2744,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56180279"/>
+        <c:crossAx val="65178294"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2733,7 +2752,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56180279"/>
+        <c:axId val="65178294"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2775,7 +2794,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43260509"/>
+        <c:crossAx val="55383104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3144,11 +3163,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="97903730"/>
-        <c:axId val="66936800"/>
+        <c:axId val="75171853"/>
+        <c:axId val="83367176"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="97903730"/>
+        <c:axId val="75171853"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3180,7 +3199,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66936800"/>
+        <c:crossAx val="83367176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3188,7 +3207,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66936800"/>
+        <c:axId val="83367176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3230,7 +3249,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97903730"/>
+        <c:crossAx val="75171853"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3523,11 +3542,11 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="0"/>
-        <c:axId val="87578632"/>
-        <c:axId val="19757056"/>
+        <c:axId val="71501548"/>
+        <c:axId val="86563054"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="87578632"/>
+        <c:axId val="71501548"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3559,7 +3578,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19757056"/>
+        <c:crossAx val="86563054"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3567,7 +3586,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19757056"/>
+        <c:axId val="86563054"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3609,7 +3628,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87578632"/>
+        <c:crossAx val="71501548"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3822,11 +3841,11 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="0"/>
-        <c:axId val="90382951"/>
-        <c:axId val="89412035"/>
+        <c:axId val="80379063"/>
+        <c:axId val="85908215"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="90382951"/>
+        <c:axId val="80379063"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3858,7 +3877,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89412035"/>
+        <c:crossAx val="85908215"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3866,7 +3885,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89412035"/>
+        <c:axId val="85908215"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3908,7 +3927,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90382951"/>
+        <c:crossAx val="80379063"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4211,11 +4230,11 @@
         </c:ser>
         <c:gapWidth val="45"/>
         <c:overlap val="0"/>
-        <c:axId val="85076720"/>
-        <c:axId val="26523048"/>
+        <c:axId val="48176604"/>
+        <c:axId val="77406514"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="85076720"/>
+        <c:axId val="48176604"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4247,7 +4266,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26523048"/>
+        <c:crossAx val="77406514"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4255,7 +4274,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26523048"/>
+        <c:axId val="77406514"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4297,7 +4316,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85076720"/>
+        <c:crossAx val="48176604"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4673,11 +4692,11 @@
         </c:ser>
         <c:gapWidth val="35"/>
         <c:overlap val="0"/>
-        <c:axId val="8322192"/>
-        <c:axId val="24441815"/>
+        <c:axId val="68539520"/>
+        <c:axId val="54088237"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="8322192"/>
+        <c:axId val="68539520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4709,7 +4728,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24441815"/>
+        <c:crossAx val="54088237"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4717,7 +4736,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24441815"/>
+        <c:axId val="54088237"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4759,7 +4778,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8322192"/>
+        <c:crossAx val="68539520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5835,7 +5854,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{AA9D944D-D23D-4EC5-96E2-BA6ED16FC22F}</x14:id>
+          <x14:id>{586C37CD-6200-4EAA-A54D-2CE8E75C2A4F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5849,7 +5868,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2B9F3834-EA8A-415C-B921-50DB70588097}</x14:id>
+          <x14:id>{4CC1FE55-B5A8-4671-81F9-10FC1A605887}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5866,7 +5885,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{AA9D944D-D23D-4EC5-96E2-BA6ED16FC22F}">
+          <x14:cfRule type="dataBar" id="{586C37CD-6200-4EAA-A54D-2CE8E75C2A4F}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5881,7 +5900,7 @@
           <xm:sqref>G56:G67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2B9F3834-EA8A-415C-B921-50DB70588097}">
+          <x14:cfRule type="dataBar" id="{4CC1FE55-B5A8-4671-81F9-10FC1A605887}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5944,7 +5963,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(8&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,8))</f>
+        <f aca="false">IF(8&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,8))</f>
         <v>46242</v>
       </c>
       <c r="B2" s="54"/>
@@ -6479,7 +6498,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(9&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,9))</f>
+        <f aca="false">IF(9&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,9))</f>
         <v>46243</v>
       </c>
       <c r="B2" s="54"/>
@@ -7028,7 +7047,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(10&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,10))</f>
+        <f aca="false">IF(10&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,10))</f>
         <v>46244</v>
       </c>
       <c r="B2" s="54"/>
@@ -7563,7 +7582,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(11&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,11))</f>
+        <f aca="false">IF(11&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,11))</f>
         <v>46245</v>
       </c>
       <c r="B2" s="54"/>
@@ -8102,7 +8121,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(12&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,12))</f>
+        <f aca="false">IF(12&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,12))</f>
         <v>46246</v>
       </c>
       <c r="B2" s="54"/>
@@ -8641,7 +8660,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(13&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,13))</f>
+        <f aca="false">IF(13&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,13))</f>
         <v>46247</v>
       </c>
       <c r="B2" s="54"/>
@@ -9176,7 +9195,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(14&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,14))</f>
+        <f aca="false">IF(14&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,14))</f>
         <v>46248</v>
       </c>
       <c r="B2" s="54"/>
@@ -9711,7 +9730,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(15&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,15))</f>
+        <f aca="false">IF(15&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,15))</f>
         <v>46249</v>
       </c>
       <c r="B2" s="54"/>
@@ -10246,7 +10265,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(16&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,16))</f>
+        <f aca="false">IF(16&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,16))</f>
         <v>46250</v>
       </c>
       <c r="B2" s="54"/>
@@ -10797,7 +10816,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(17&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,17))</f>
+        <f aca="false">IF(17&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,17))</f>
         <v>46251</v>
       </c>
       <c r="B2" s="54"/>
@@ -13302,7 +13321,7 @@
         <v>4223</v>
       </c>
       <c r="M40" s="28" t="n">
-        <f aca="false">$M39</f>
+        <f aca="false">INDEX($M$9:$M$39,$F$4)</f>
         <v>4223</v>
       </c>
       <c r="N40" s="28" t="n">
@@ -13407,7 +13426,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E0F78625-A050-47A5-8D31-15D1F8F5A9E8}</x14:id>
+          <x14:id>{8012C650-5B2A-41D1-BFB0-9D23A2BAB0E5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -13429,7 +13448,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E0F78625-A050-47A5-8D31-15D1F8F5A9E8}">
+          <x14:cfRule type="dataBar" id="{8012C650-5B2A-41D1-BFB0-9D23A2BAB0E5}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13492,7 +13511,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(18&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,18))</f>
+        <f aca="false">IF(18&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,18))</f>
         <v>46252</v>
       </c>
       <c r="B2" s="54"/>
@@ -14027,7 +14046,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(19&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,19))</f>
+        <f aca="false">IF(19&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,19))</f>
         <v>46253</v>
       </c>
       <c r="B2" s="54"/>
@@ -14566,7 +14585,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(20&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,20))</f>
+        <f aca="false">IF(20&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,20))</f>
         <v>46254</v>
       </c>
       <c r="B2" s="54"/>
@@ -15105,7 +15124,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(21&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,21))</f>
+        <f aca="false">IF(21&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,21))</f>
         <v>46255</v>
       </c>
       <c r="B2" s="54"/>
@@ -15640,7 +15659,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(22&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,22))</f>
+        <f aca="false">IF(22&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,22))</f>
         <v>46256</v>
       </c>
       <c r="B2" s="54"/>
@@ -16179,7 +16198,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(23&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,23))</f>
+        <f aca="false">IF(23&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,23))</f>
         <v>46257</v>
       </c>
       <c r="B2" s="54"/>
@@ -16728,7 +16747,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(24&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,24))</f>
+        <f aca="false">IF(24&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,24))</f>
         <v>46258</v>
       </c>
       <c r="B2" s="54"/>
@@ -17265,7 +17284,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(25&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,25))</f>
+        <f aca="false">IF(25&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,25))</f>
         <v>46259</v>
       </c>
       <c r="B2" s="54"/>
@@ -17804,7 +17823,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(26&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,26))</f>
+        <f aca="false">IF(26&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,26))</f>
         <v>46260</v>
       </c>
       <c r="B2" s="54"/>
@@ -18343,7 +18362,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(27&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,27))</f>
+        <f aca="false">IF(27&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,27))</f>
         <v>46261</v>
       </c>
       <c r="B2" s="54"/>
@@ -18878,7 +18897,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(1&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,1))</f>
+        <f aca="false">IF(1&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,1))</f>
         <v>46235</v>
       </c>
       <c r="B2" s="54"/>
@@ -19343,12 +19362,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Choisissez dans la liste, ou tapez un nouveau nom." promptTitle="Fournisseur" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="B12:B25" type="list">
+      <formula1>LISTES!$A$2:$A$19</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Tapez un nombre de dirhams, sans texte." errorStyle="stop" errorTitle="Montant invalide" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C12:C25 F12:F25 I12:I25 L12:L25" type="decimal">
       <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Choisissez dans la liste, ou tapez un nouveau nom." promptTitle="Fournisseur" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="B12:B25" type="list">
-      <formula1>LISTES!$A$2:$A$19</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E20:E25" type="list">
@@ -19418,7 +19437,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(28&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,28))</f>
+        <f aca="false">IF(28&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,28))</f>
         <v>46262</v>
       </c>
       <c r="B2" s="54"/>
@@ -19939,7 +19958,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(29&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,29))</f>
+        <f aca="false">IF(29&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,29))</f>
         <v>46263</v>
       </c>
       <c r="B2" s="54"/>
@@ -20460,7 +20479,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(30&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,30))</f>
+        <f aca="false">IF(30&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,30))</f>
         <v>46264</v>
       </c>
       <c r="B2" s="54"/>
@@ -20981,7 +21000,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(31&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,31))</f>
+        <f aca="false">IF(31&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,31))</f>
         <v>46265</v>
       </c>
       <c r="B2" s="54"/>
@@ -21465,7 +21484,7 @@
     <tabColor rgb="FFB26A00"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:F43"/>
+  <dimension ref="B1:F44"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -22030,8 +22049,7 @@
         <v>136</v>
       </c>
       <c r="C39" s="96" t="n">
-        <f aca="false">IFERROR(($C$13+$C$27+$C$30+$C$33)/30,0)</f>
-        <v>2284.3</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22039,8 +22057,8 @@
         <v>137</v>
       </c>
       <c r="C40" s="97" t="n">
-        <f aca="false">IFERROR('RECAP DU JOURNAL'!$F$40/COUNTIF('RECAP DU JOURNAL'!$F$9:$F$39,"&gt;0"),0)</f>
-        <v>2034.7037037037</v>
+        <f aca="false">IFERROR(($C$13+$C$27+$C$39)/30,0)</f>
+        <v>1983.33333333333</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22048,18 +22066,27 @@
         <v>138</v>
       </c>
       <c r="C41" s="98" t="n">
-        <f aca="false">$C$40-$C$39</f>
-        <v>-249.596296296297</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="30" t="s">
+        <f aca="false">IFERROR('RECAP DU JOURNAL'!$F$40/COUNTIF('RECAP DU JOURNAL'!$F$9:$F$39,"&gt;0"),0)</f>
+        <v>2034.7037037037</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="95" t="s">
         <v>139</v>
       </c>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
+      <c r="C42" s="99" t="n">
+        <f aca="false">$C$41-$C$40</f>
+        <v>51.3703703703704</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -22068,7 +22095,7 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B44:F44"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F12">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
@@ -22097,7 +22124,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41">
+  <conditionalFormatting sqref="C42">
     <cfRule type="cellIs" priority="9" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>0</formula>
     </cfRule>
@@ -22135,7 +22162,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -22147,7 +22174,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -22159,32 +22186,32 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G4" s="18" t="s">
         <v>64</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="99" t="n">
+      <c r="B5" s="100" t="n">
         <f aca="false">DATE('RECAP DU JOURNAL'!$C$3,1,1)</f>
         <v>46023</v>
       </c>
@@ -22196,7 +22223,7 @@
         <f aca="false">IF(MONTH($B5)='RECAP DU JOURNAL'!$C$4,'RECAP DU JOURNAL'!$G$40,0)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="100" t="n">
+      <c r="E5" s="101" t="n">
         <f aca="false">IFERROR($D5/$C5,0)</f>
         <v>0</v>
       </c>
@@ -22208,7 +22235,7 @@
         <f aca="false">$D5+$F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="101" t="n">
+      <c r="H5" s="102" t="n">
         <f aca="false">IFERROR(($C5-$G5)/$C5,0)</f>
         <v>0</v>
       </c>
@@ -22218,7 +22245,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="102" t="n">
+      <c r="B6" s="103" t="n">
         <f aca="false">DATE('RECAP DU JOURNAL'!$C$3,2,1)</f>
         <v>46054</v>
       </c>
@@ -22230,7 +22257,7 @@
         <f aca="false">IF(MONTH($B6)='RECAP DU JOURNAL'!$C$4,'RECAP DU JOURNAL'!$G$40,0)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="103" t="n">
+      <c r="E6" s="104" t="n">
         <f aca="false">IFERROR($D6/$C6,0)</f>
         <v>0</v>
       </c>
@@ -22242,7 +22269,7 @@
         <f aca="false">$D6+$F6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="104" t="n">
+      <c r="H6" s="105" t="n">
         <f aca="false">IFERROR(($C6-$G6)/$C6,0)</f>
         <v>0</v>
       </c>
@@ -22252,7 +22279,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="99" t="n">
+      <c r="B7" s="100" t="n">
         <f aca="false">DATE('RECAP DU JOURNAL'!$C$3,3,1)</f>
         <v>46082</v>
       </c>
@@ -22264,7 +22291,7 @@
         <f aca="false">IF(MONTH($B7)='RECAP DU JOURNAL'!$C$4,'RECAP DU JOURNAL'!$G$40,0)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="100" t="n">
+      <c r="E7" s="101" t="n">
         <f aca="false">IFERROR($D7/$C7,0)</f>
         <v>0</v>
       </c>
@@ -22276,7 +22303,7 @@
         <f aca="false">$D7+$F7</f>
         <v>0</v>
       </c>
-      <c r="H7" s="101" t="n">
+      <c r="H7" s="102" t="n">
         <f aca="false">IFERROR(($C7-$G7)/$C7,0)</f>
         <v>0</v>
       </c>
@@ -22286,7 +22313,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="102" t="n">
+      <c r="B8" s="103" t="n">
         <f aca="false">DATE('RECAP DU JOURNAL'!$C$3,4,1)</f>
         <v>46113</v>
       </c>
@@ -22298,7 +22325,7 @@
         <f aca="false">IF(MONTH($B8)='RECAP DU JOURNAL'!$C$4,'RECAP DU JOURNAL'!$G$40,0)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="103" t="n">
+      <c r="E8" s="104" t="n">
         <f aca="false">IFERROR($D8/$C8,0)</f>
         <v>0</v>
       </c>
@@ -22310,7 +22337,7 @@
         <f aca="false">$D8+$F8</f>
         <v>0</v>
       </c>
-      <c r="H8" s="104" t="n">
+      <c r="H8" s="105" t="n">
         <f aca="false">IFERROR(($C8-$G8)/$C8,0)</f>
         <v>0</v>
       </c>
@@ -22320,7 +22347,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="99" t="n">
+      <c r="B9" s="100" t="n">
         <f aca="false">DATE('RECAP DU JOURNAL'!$C$3,5,1)</f>
         <v>46143</v>
       </c>
@@ -22332,7 +22359,7 @@
         <f aca="false">IF(MONTH($B9)='RECAP DU JOURNAL'!$C$4,'RECAP DU JOURNAL'!$G$40,0)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="100" t="n">
+      <c r="E9" s="101" t="n">
         <f aca="false">IFERROR($D9/$C9,0)</f>
         <v>0</v>
       </c>
@@ -22344,7 +22371,7 @@
         <f aca="false">$D9+$F9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="101" t="n">
+      <c r="H9" s="102" t="n">
         <f aca="false">IFERROR(($C9-$G9)/$C9,0)</f>
         <v>0</v>
       </c>
@@ -22354,7 +22381,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="102" t="n">
+      <c r="B10" s="103" t="n">
         <f aca="false">DATE('RECAP DU JOURNAL'!$C$3,6,1)</f>
         <v>46174</v>
       </c>
@@ -22366,7 +22393,7 @@
         <f aca="false">IF(MONTH($B10)='RECAP DU JOURNAL'!$C$4,'RECAP DU JOURNAL'!$G$40,0)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="103" t="n">
+      <c r="E10" s="104" t="n">
         <f aca="false">IFERROR($D10/$C10,0)</f>
         <v>0</v>
       </c>
@@ -22378,7 +22405,7 @@
         <f aca="false">$D10+$F10</f>
         <v>0</v>
       </c>
-      <c r="H10" s="104" t="n">
+      <c r="H10" s="105" t="n">
         <f aca="false">IFERROR(($C10-$G10)/$C10,0)</f>
         <v>0</v>
       </c>
@@ -22388,7 +22415,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="99" t="n">
+      <c r="B11" s="100" t="n">
         <f aca="false">DATE('RECAP DU JOURNAL'!$C$3,7,1)</f>
         <v>46204</v>
       </c>
@@ -22400,7 +22427,7 @@
         <f aca="false">IF(MONTH($B11)='RECAP DU JOURNAL'!$C$4,'RECAP DU JOURNAL'!$G$40,0)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="100" t="n">
+      <c r="E11" s="101" t="n">
         <f aca="false">IFERROR($D11/$C11,0)</f>
         <v>0</v>
       </c>
@@ -22412,7 +22439,7 @@
         <f aca="false">$D11+$F11</f>
         <v>0</v>
       </c>
-      <c r="H11" s="101" t="n">
+      <c r="H11" s="102" t="n">
         <f aca="false">IFERROR(($C11-$G11)/$C11,0)</f>
         <v>0</v>
       </c>
@@ -22422,7 +22449,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="102" t="n">
+      <c r="B12" s="103" t="n">
         <f aca="false">DATE('RECAP DU JOURNAL'!$C$3,8,1)</f>
         <v>46235</v>
       </c>
@@ -22434,7 +22461,7 @@
         <f aca="false">IF(MONTH($B12)='RECAP DU JOURNAL'!$C$4,'RECAP DU JOURNAL'!$G$40,0)</f>
         <v>24529</v>
       </c>
-      <c r="E12" s="103" t="n">
+      <c r="E12" s="104" t="n">
         <f aca="false">IFERROR($D12/$C12,0)</f>
         <v>0.446493255911317</v>
       </c>
@@ -22446,7 +22473,7 @@
         <f aca="false">$D12+$F12</f>
         <v>50714</v>
       </c>
-      <c r="H12" s="104" t="n">
+      <c r="H12" s="105" t="n">
         <f aca="false">IFERROR(($C12-$G12)/$C12,0)</f>
         <v>0.0768698691228134</v>
       </c>
@@ -22456,7 +22483,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="99" t="n">
+      <c r="B13" s="100" t="n">
         <f aca="false">DATE('RECAP DU JOURNAL'!$C$3,9,1)</f>
         <v>46266</v>
       </c>
@@ -22468,7 +22495,7 @@
         <f aca="false">IF(MONTH($B13)='RECAP DU JOURNAL'!$C$4,'RECAP DU JOURNAL'!$G$40,0)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="100" t="n">
+      <c r="E13" s="101" t="n">
         <f aca="false">IFERROR($D13/$C13,0)</f>
         <v>0</v>
       </c>
@@ -22480,7 +22507,7 @@
         <f aca="false">$D13+$F13</f>
         <v>0</v>
       </c>
-      <c r="H13" s="101" t="n">
+      <c r="H13" s="102" t="n">
         <f aca="false">IFERROR(($C13-$G13)/$C13,0)</f>
         <v>0</v>
       </c>
@@ -22490,7 +22517,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="102" t="n">
+      <c r="B14" s="103" t="n">
         <f aca="false">DATE('RECAP DU JOURNAL'!$C$3,10,1)</f>
         <v>46296</v>
       </c>
@@ -22502,7 +22529,7 @@
         <f aca="false">IF(MONTH($B14)='RECAP DU JOURNAL'!$C$4,'RECAP DU JOURNAL'!$G$40,0)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="103" t="n">
+      <c r="E14" s="104" t="n">
         <f aca="false">IFERROR($D14/$C14,0)</f>
         <v>0</v>
       </c>
@@ -22514,7 +22541,7 @@
         <f aca="false">$D14+$F14</f>
         <v>0</v>
       </c>
-      <c r="H14" s="104" t="n">
+      <c r="H14" s="105" t="n">
         <f aca="false">IFERROR(($C14-$G14)/$C14,0)</f>
         <v>0</v>
       </c>
@@ -22524,7 +22551,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="99" t="n">
+      <c r="B15" s="100" t="n">
         <f aca="false">DATE('RECAP DU JOURNAL'!$C$3,11,1)</f>
         <v>46327</v>
       </c>
@@ -22536,7 +22563,7 @@
         <f aca="false">IF(MONTH($B15)='RECAP DU JOURNAL'!$C$4,'RECAP DU JOURNAL'!$G$40,0)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="100" t="n">
+      <c r="E15" s="101" t="n">
         <f aca="false">IFERROR($D15/$C15,0)</f>
         <v>0</v>
       </c>
@@ -22548,7 +22575,7 @@
         <f aca="false">$D15+$F15</f>
         <v>0</v>
       </c>
-      <c r="H15" s="101" t="n">
+      <c r="H15" s="102" t="n">
         <f aca="false">IFERROR(($C15-$G15)/$C15,0)</f>
         <v>0</v>
       </c>
@@ -22558,7 +22585,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="102" t="n">
+      <c r="B16" s="103" t="n">
         <f aca="false">DATE('RECAP DU JOURNAL'!$C$3,12,1)</f>
         <v>46357</v>
       </c>
@@ -22570,7 +22597,7 @@
         <f aca="false">IF(MONTH($B16)='RECAP DU JOURNAL'!$C$4,'RECAP DU JOURNAL'!$G$40,0)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="103" t="n">
+      <c r="E16" s="104" t="n">
         <f aca="false">IFERROR($D16/$C16,0)</f>
         <v>0</v>
       </c>
@@ -22582,7 +22609,7 @@
         <f aca="false">$D16+$F16</f>
         <v>0</v>
       </c>
-      <c r="H16" s="104" t="n">
+      <c r="H16" s="105" t="n">
         <f aca="false">IFERROR(($C16-$G16)/$C16,0)</f>
         <v>0</v>
       </c>
@@ -22593,7 +22620,7 @@
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17" s="28" t="n">
         <f aca="false">SUM(C5:C16)</f>
@@ -22626,7 +22653,7 @@
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -22634,199 +22661,199 @@
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D20" s="18" t="s">
         <v>60</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="105" t="n">
+      <c r="B21" s="106" t="n">
         <v>45658</v>
       </c>
-      <c r="C21" s="106" t="n">
+      <c r="C21" s="107" t="n">
         <v>58097</v>
       </c>
-      <c r="D21" s="106" t="n">
+      <c r="D21" s="107" t="n">
         <v>17550</v>
       </c>
-      <c r="E21" s="107" t="n">
+      <c r="E21" s="108" t="n">
         <f aca="false">IFERROR($D21/$C21,0)</f>
         <v>0.302081002461401</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="108" t="n">
+      <c r="B22" s="109" t="n">
         <v>45689</v>
       </c>
-      <c r="C22" s="109" t="n">
+      <c r="C22" s="110" t="n">
         <v>47774</v>
       </c>
-      <c r="D22" s="109" t="n">
+      <c r="D22" s="110" t="n">
         <v>15723</v>
       </c>
-      <c r="E22" s="110" t="n">
+      <c r="E22" s="111" t="n">
         <f aca="false">IFERROR($D22/$C22,0)</f>
         <v>0.329112069326412</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="105" t="n">
+      <c r="B23" s="106" t="n">
         <v>45717</v>
       </c>
-      <c r="C23" s="106" t="n">
+      <c r="C23" s="107" t="n">
         <v>33629</v>
       </c>
-      <c r="D23" s="106" t="n">
+      <c r="D23" s="107" t="n">
         <v>19497</v>
       </c>
-      <c r="E23" s="107" t="n">
+      <c r="E23" s="108" t="n">
         <f aca="false">IFERROR($D23/$C23,0)</f>
         <v>0.579767462606679</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="108" t="n">
+      <c r="B24" s="109" t="n">
         <v>45748</v>
       </c>
-      <c r="C24" s="109" t="n">
+      <c r="C24" s="110" t="n">
         <v>63101</v>
       </c>
-      <c r="D24" s="109" t="n">
+      <c r="D24" s="110" t="n">
         <v>24871</v>
       </c>
-      <c r="E24" s="110" t="n">
+      <c r="E24" s="111" t="n">
         <f aca="false">IFERROR($D24/$C24,0)</f>
         <v>0.394145893092027</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="105" t="n">
+      <c r="B25" s="106" t="n">
         <v>45778</v>
       </c>
-      <c r="C25" s="106" t="n">
+      <c r="C25" s="107" t="n">
         <v>67697</v>
       </c>
-      <c r="D25" s="106" t="n">
+      <c r="D25" s="107" t="n">
         <v>27947</v>
       </c>
-      <c r="E25" s="107" t="n">
+      <c r="E25" s="108" t="n">
         <f aca="false">IFERROR($D25/$C25,0)</f>
         <v>0.412824792826861</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="108" t="n">
+      <c r="B26" s="109" t="n">
         <v>45809</v>
       </c>
-      <c r="C26" s="109" t="n">
+      <c r="C26" s="110" t="n">
         <v>57443</v>
       </c>
-      <c r="D26" s="109" t="n">
+      <c r="D26" s="110" t="n">
         <v>23534</v>
       </c>
-      <c r="E26" s="110" t="n">
+      <c r="E26" s="111" t="n">
         <f aca="false">IFERROR($D26/$C26,0)</f>
         <v>0.409693087060216</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="105" t="n">
+      <c r="B27" s="106" t="n">
         <v>45839</v>
       </c>
-      <c r="C27" s="106" t="n">
+      <c r="C27" s="107" t="n">
         <v>71948</v>
       </c>
-      <c r="D27" s="106" t="n">
+      <c r="D27" s="107" t="n">
         <v>28425</v>
       </c>
-      <c r="E27" s="107" t="n">
+      <c r="E27" s="108" t="n">
         <f aca="false">IFERROR($D27/$C27,0)</f>
         <v>0.395077000055596</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="108" t="n">
+      <c r="B28" s="109" t="n">
         <v>45870</v>
       </c>
-      <c r="C28" s="109" t="n">
+      <c r="C28" s="110" t="n">
         <v>78294</v>
       </c>
-      <c r="D28" s="109" t="n">
+      <c r="D28" s="110" t="n">
         <v>31683</v>
       </c>
-      <c r="E28" s="110" t="n">
+      <c r="E28" s="111" t="n">
         <f aca="false">IFERROR($D28/$C28,0)</f>
         <v>0.404667024293049</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="105" t="n">
+      <c r="B29" s="106" t="n">
         <v>45901</v>
       </c>
-      <c r="C29" s="106" t="n">
+      <c r="C29" s="107" t="n">
         <v>53925</v>
       </c>
-      <c r="D29" s="106" t="n">
+      <c r="D29" s="107" t="n">
         <v>23474</v>
       </c>
-      <c r="E29" s="107" t="n">
+      <c r="E29" s="108" t="n">
         <f aca="false">IFERROR($D29/$C29,0)</f>
         <v>0.435308298562819</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="108" t="n">
+      <c r="B30" s="109" t="n">
         <v>45931</v>
       </c>
-      <c r="C30" s="109" t="n">
+      <c r="C30" s="110" t="n">
         <v>52669</v>
       </c>
-      <c r="D30" s="109" t="n">
+      <c r="D30" s="110" t="n">
         <v>22122</v>
       </c>
-      <c r="E30" s="110" t="n">
+      <c r="E30" s="111" t="n">
         <f aca="false">IFERROR($D30/$C30,0)</f>
         <v>0.42001936623061</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="105" t="n">
+      <c r="B31" s="106" t="n">
         <v>45962</v>
       </c>
-      <c r="C31" s="106"/>
-      <c r="D31" s="106"/>
-      <c r="E31" s="107" t="n">
+      <c r="C31" s="107"/>
+      <c r="D31" s="107"/>
+      <c r="E31" s="108" t="n">
         <f aca="false">IFERROR($D31/$C31,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="108" t="n">
+      <c r="B32" s="109" t="n">
         <v>45992</v>
       </c>
-      <c r="C32" s="109"/>
-      <c r="D32" s="109"/>
-      <c r="E32" s="110" t="n">
+      <c r="C32" s="110"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="111" t="n">
         <f aca="false">IFERROR($D32/$C32,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="C33" s="111" t="n">
+        <v>152</v>
+      </c>
+      <c r="C33" s="112" t="n">
         <f aca="false">SUM(C21:C32)</f>
         <v>584577</v>
       </c>
-      <c r="D33" s="111" t="n">
+      <c r="D33" s="112" t="n">
         <f aca="false">SUM(D21:D32)</f>
         <v>234826</v>
       </c>
@@ -22837,7 +22864,7 @@
     </row>
     <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C35" s="30"/>
       <c r="D35" s="30"/>
@@ -22868,7 +22895,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65DC47FF-B3E9-4E43-96D9-2BB25D698C70}</x14:id>
+          <x14:id>{41BE258D-BAD9-465E-8C25-B61EB7C96254}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22897,7 +22924,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{65DC47FF-B3E9-4E43-96D9-2BB25D698C70}">
+          <x14:cfRule type="dataBar" id="{41BE258D-BAD9-465E-8C25-B61EB7C96254}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -22930,20 +22957,20 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="112" t="s">
-        <v>153</v>
-      </c>
-      <c r="B1" s="112" t="s">
+      <c r="A1" s="113" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="113" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="112" t="s">
-        <v>154</v>
-      </c>
-      <c r="D1" s="112" t="s">
+      <c r="C1" s="113" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="113" t="s">
-        <v>155</v>
+      <c r="F1" s="114" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22959,8 +22986,8 @@
       <c r="D2" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="113" t="s">
-        <v>156</v>
+      <c r="F2" s="114" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23035,7 +23062,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>99</v>
@@ -23057,7 +23084,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>103</v>
@@ -23065,7 +23092,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>104</v>
@@ -23081,12 +23108,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23111,7 +23138,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -23168,7 +23195,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(2&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,2))</f>
+        <f aca="false">IF(2&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,2))</f>
         <v>46236</v>
       </c>
       <c r="B2" s="54"/>
@@ -23643,12 +23670,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
+    <dataValidation allowBlank="true" error="Tapez un nombre de dirhams, sans texte." errorStyle="stop" errorTitle="Montant invalide" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C12:C25 F12:F25 I12:I25 L12:L25" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Choisissez dans la liste, ou tapez un nouveau nom." promptTitle="Fournisseur" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="B12:B25" type="list">
       <formula1>LISTES!$A$2:$A$19</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Tapez un nombre de dirhams, sans texte." errorStyle="stop" errorTitle="Montant invalide" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C12:C25 F12:F25 I12:I25 L12:L25" type="decimal">
-      <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E20:E25" type="list">
@@ -23717,7 +23744,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(3&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,3))</f>
+        <f aca="false">IF(3&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,3))</f>
         <v>46237</v>
       </c>
       <c r="B2" s="54"/>
@@ -24252,7 +24279,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(4&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,4))</f>
+        <f aca="false">IF(4&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,4))</f>
         <v>46238</v>
       </c>
       <c r="B2" s="54"/>
@@ -24791,7 +24818,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(5&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,5))</f>
+        <f aca="false">IF(5&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,5))</f>
         <v>46239</v>
       </c>
       <c r="B2" s="54"/>
@@ -25330,7 +25357,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(6&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,6))</f>
+        <f aca="false">IF(6&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,6))</f>
         <v>46240</v>
       </c>
       <c r="B2" s="54"/>
@@ -25865,7 +25892,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="54" t="n">
-        <f aca="false">IF(7&gt;'RECAP DU JOURNAL'!$F$4,"",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,7))</f>
+        <f aca="false">IF(7&gt;'RECAP DU JOURNAL'!$F$4,"— ce jour n'existe pas dans le mois —",DATE('RECAP DU JOURNAL'!$C$3,'RECAP DU JOURNAL'!$C$4,7))</f>
         <v>46241</v>
       </c>
       <c r="B2" s="54"/>
